--- a/谱图/报告解析/称量记录.xlsx
+++ b/谱图/报告解析/称量记录.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA6DF05-035B-4CCD-AA47-F4A0E7D7F912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D80F31-FB86-467C-AB6B-E1E8699F3489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>称样时间</t>
   </si>
@@ -35,7 +35,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TS26072901</t>
+    <t>TS26072956006A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TS26072956006B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -426,9 +431,18 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="A3" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>0.5212</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
